--- a/data/individuals_sheet_och.xlsx
+++ b/data/individuals_sheet_och.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/!students/Ty_Burris_Thesis/Data Analysis/och_cross-contam_testing/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbird\Downloads\pire_ostorhinchus_chrysopomus_lcwgs_cross-contam\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1757D1E8-804D-467A-A793-90E2B7E6A011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B068C7CF-8711-42A0-A2DF-F0193BF53B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24975" yWindow="-28965" windowWidth="16440" windowHeight="28320" xr2:uid="{486CE9F8-A468-4019-ABC1-A5E08A78DB35}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{486CE9F8-A468-4019-ABC1-A5E08A78DB35}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1499,9 +1499,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1838,45 +1841,48 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8AB3B61-9259-4F02-B2A1-B77CB04F7389}">
   <dimension ref="A1:M351"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="3" max="3" width="12.9453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
